--- a/samples/reference-tables/Price/MegaPrice.xlsx
+++ b/samples/reference-tables/Price/MegaPrice.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="218">
   <si>
     <t>id</t>
   </si>
@@ -224,6 +224,9 @@
     <t>bookreact.jpg,bookreact2.jpg</t>
   </si>
   <si>
+    <t>requires focused reading</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
@@ -278,6 +281,9 @@
     <t>zip package</t>
   </si>
   <si>
+    <t>easy to read</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -314,6 +320,9 @@
     <t>box</t>
   </si>
   <si>
+    <t>delicate taste</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
@@ -326,6 +335,9 @@
     <t>18 inches</t>
   </si>
   <si>
+    <t>very spicy</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
@@ -359,6 +371,9 @@
     <t>aesthetic packaging</t>
   </si>
   <si>
+    <t>classic</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
@@ -392,6 +407,9 @@
     <t>https://lh3.googleusercontent.com/pw/AP1GczOndj66CgQrW-RXbSRf7VgJe2A_Sae7eCqxWlSZEBFtpUpaQZScYgpf-SwIA0vlEgs4FtP2etmyHXQOYQpsERWRlEbi7DKL8vC9AvU5NEYzFA0iIg=w2400</t>
   </si>
   <si>
+    <t>simple</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
@@ -413,6 +431,9 @@
     <t>sneakerswhite.jpg,sneakerswhite2.jpg</t>
   </si>
   <si>
+    <t>complex details</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
@@ -539,7 +560,7 @@
     <t>about</t>
   </si>
   <si>
-    <t>Артикл</t>
+    <t>Article</t>
   </si>
   <si>
     <t>Автор:</t>
@@ -584,7 +605,10 @@
     <t>Калории:</t>
   </si>
   <si>
-    <t>Упаковка</t>
+    <t>package</t>
+  </si>
+  <si>
+    <t>book~ease of reading;pizza~taste;shoes~design;</t>
   </si>
   <si>
     <t>Size is basical</t>
@@ -693,6 +717,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9.0"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans&quot;"/>
@@ -718,11 +747,6 @@
       <sz val="9.0"/>
       <color rgb="FF1155CC"/>
       <name val="&quot;Google Sans&quot;"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -890,7 +914,10 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -899,10 +926,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -911,23 +938,20 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="7" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="7" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="7" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -937,15 +961,15 @@
     <xf borderId="0" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1520,7 +1544,9 @@
       <c r="X5" s="11"/>
       <c r="Y5" s="16"/>
       <c r="Z5" s="11"/>
-      <c r="AA5" s="11"/>
+      <c r="AA5" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="13">
         <v>19.0</v>
@@ -1532,42 +1558,42 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="M6" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="M6" s="19" t="s">
         <v>49</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>67</v>
@@ -1578,18 +1604,18 @@
       <c r="Q6" s="16"/>
       <c r="R6" s="6"/>
       <c r="S6" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T6" s="6"/>
       <c r="U6" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V6" s="14"/>
       <c r="W6" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y6" s="16"/>
       <c r="Z6" s="6"/>
@@ -1603,7 +1629,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>31</v>
@@ -1622,7 +1648,7 @@
         <v>57</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>59</v>
@@ -1639,7 +1665,7 @@
       <c r="Q7" s="16"/>
       <c r="R7" s="6"/>
       <c r="S7" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="12" t="s">
@@ -1652,9 +1678,11 @@
       </c>
       <c r="Y7" s="16"/>
       <c r="Z7" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA7" s="11"/>
+        <v>88</v>
+      </c>
+      <c r="AA7" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="13"/>
       <c r="AD7" s="6"/>
@@ -1664,37 +1692,37 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="20"/>
+        <v>91</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="2"/>
       <c r="F8" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I8" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="J8" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>91</v>
-      </c>
       <c r="L8" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4" t="s">
@@ -1702,15 +1730,15 @@
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
       <c r="U8" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="V8" s="14"/>
       <c r="W8" s="11">
@@ -1719,9 +1747,11 @@
       <c r="X8" s="11"/>
       <c r="Y8" s="16"/>
       <c r="Z8" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA8" s="11"/>
+        <v>101</v>
+      </c>
+      <c r="AA8" s="18" t="s">
+        <v>102</v>
+      </c>
       <c r="AB8" s="11"/>
       <c r="AC8" s="13">
         <v>5.0</v>
@@ -1733,34 +1763,34 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="2"/>
       <c r="F9" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I9" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>91</v>
-      </c>
       <c r="L9" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M9" s="11"/>
       <c r="N9" s="2"/>
@@ -1769,15 +1799,15 @@
       </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
       <c r="U9" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="V9" s="14"/>
       <c r="W9" s="11">
@@ -1786,9 +1816,11 @@
       <c r="X9" s="6"/>
       <c r="Y9" s="16"/>
       <c r="Z9" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA9" s="11"/>
+        <v>101</v>
+      </c>
+      <c r="AA9" s="18" t="s">
+        <v>107</v>
+      </c>
       <c r="AB9" s="11"/>
       <c r="AC9" s="13">
         <v>5.0</v>
@@ -1800,35 +1832,35 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="2"/>
       <c r="F10" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="11"/>
       <c r="J10" s="13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="4" t="s">
@@ -1839,25 +1871,27 @@
         <v>34.0</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="15" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="V10" s="17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="W10" s="11"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="16"/>
       <c r="Z10" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA10" s="11"/>
+        <v>118</v>
+      </c>
+      <c r="AA10" s="18" t="s">
+        <v>119</v>
+      </c>
       <c r="AB10" s="11"/>
       <c r="AC10" s="13">
         <v>2.0</v>
@@ -1869,35 +1903,35 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="2"/>
       <c r="F11" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="6"/>
       <c r="J11" s="13" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="4" t="s">
@@ -1908,23 +1942,25 @@
         <v>36.0</v>
       </c>
       <c r="R11" s="11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="S11" s="11" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="T11" s="6"/>
       <c r="U11" s="15"/>
       <c r="V11" s="17" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
       <c r="Y11" s="16"/>
       <c r="Z11" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA11" s="11"/>
+        <v>118</v>
+      </c>
+      <c r="AA11" s="18" t="s">
+        <v>119</v>
+      </c>
       <c r="AB11" s="11"/>
       <c r="AC11" s="13"/>
       <c r="AD11" s="11" t="s">
@@ -1936,30 +1972,30 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="2"/>
       <c r="F12" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="2"/>
       <c r="I12" s="6"/>
       <c r="J12" s="13" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M12" s="11"/>
       <c r="N12" s="2"/>
@@ -1970,18 +2006,20 @@
       </c>
       <c r="R12" s="11"/>
       <c r="S12" s="11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="V12" s="17"/>
       <c r="W12" s="6"/>
       <c r="X12" s="6"/>
       <c r="Y12" s="16"/>
       <c r="Z12" s="6"/>
-      <c r="AA12" s="11"/>
+      <c r="AA12" s="18" t="s">
+        <v>131</v>
+      </c>
       <c r="AB12" s="11"/>
       <c r="AC12" s="13"/>
       <c r="AD12" s="11"/>
@@ -1991,37 +2029,37 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="11" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2031,22 +2069,24 @@
       </c>
       <c r="R13" s="6"/>
       <c r="S13" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="U13" s="15"/>
       <c r="V13" s="17" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="W13" s="6"/>
       <c r="X13" s="6"/>
       <c r="Y13" s="16"/>
       <c r="Z13" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA13" s="11"/>
+        <v>101</v>
+      </c>
+      <c r="AA13" s="18" t="s">
+        <v>139</v>
+      </c>
       <c r="AB13" s="11"/>
       <c r="AC13" s="13"/>
       <c r="AD13" s="6"/>
@@ -2056,32 +2096,32 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="11" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="M14" s="11"/>
       <c r="N14" s="2"/>
@@ -2091,23 +2131,23 @@
         <v>44.0</v>
       </c>
       <c r="R14" s="11" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="S14" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="T14" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="T14" s="11" t="s">
-        <v>131</v>
       </c>
       <c r="U14" s="15"/>
       <c r="V14" s="17" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="W14" s="6"/>
       <c r="X14" s="6"/>
       <c r="Y14" s="16"/>
       <c r="Z14" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
@@ -2121,30 +2161,30 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="2"/>
       <c r="F15" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="11" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J15" s="16"/>
       <c r="K15" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="M15" s="11"/>
       <c r="N15" s="2"/>
@@ -2154,23 +2194,23 @@
         <v>33.0</v>
       </c>
       <c r="R15" s="11" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="S15" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="T15" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="T15" s="11" t="s">
-        <v>131</v>
       </c>
       <c r="U15" s="15"/>
       <c r="V15" s="17" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="W15" s="6"/>
       <c r="X15" s="6"/>
       <c r="Y15" s="16"/>
       <c r="Z15" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
@@ -2378,8 +2418,8 @@
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
       <c r="T21" s="6"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="22"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="23"/>
       <c r="W21" s="6"/>
       <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
@@ -2395,7 +2435,7 @@
     <row r="22">
       <c r="A22" s="2"/>
       <c r="B22" s="4"/>
-      <c r="C22" s="23"/>
+      <c r="C22" s="24"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="4"/>
@@ -2413,8 +2453,8 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="26"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
       <c r="Y22" s="6"/>
@@ -2430,9 +2470,9 @@
     <row r="23">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="2"/>
       <c r="G23" s="4"/>
       <c r="H23" s="2"/>
@@ -2448,8 +2488,8 @@
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
       <c r="T23" s="6"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="26"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
       <c r="Y23" s="6"/>
@@ -2463,30 +2503,30 @@
       <c r="AG23" s="6"/>
     </row>
     <row r="24">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="29"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="29"/>
+      <c r="H24" s="31"/>
+      <c r="O24" s="31"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="30"/>
       <c r="AD24" s="6"/>
       <c r="AE24" s="6"/>
       <c r="AF24" s="6"/>
       <c r="AG24" s="6"/>
     </row>
     <row r="25">
-      <c r="A25" s="27"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="30"/>
-      <c r="K25" s="31"/>
-      <c r="O25" s="18"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
+      <c r="A25" s="28"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="31"/>
+      <c r="K25" s="18"/>
+      <c r="O25" s="19"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
       <c r="S25" s="6"/>
       <c r="AD25" s="6"/>
       <c r="AE25" s="6"/>
@@ -2494,24 +2534,24 @@
       <c r="AG25" s="6"/>
     </row>
     <row r="26">
-      <c r="A26" s="27"/>
-      <c r="D26" s="30"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="U26" s="30"/>
+      <c r="A26" s="28"/>
+      <c r="D26" s="31"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="U26" s="31"/>
       <c r="AD26" s="6"/>
       <c r="AE26" s="6"/>
       <c r="AF26" s="6"/>
       <c r="AG26" s="6"/>
     </row>
     <row r="27">
-      <c r="A27" s="27"/>
+      <c r="A27" s="28"/>
       <c r="D27" s="32"/>
       <c r="G27" s="33"/>
       <c r="I27" s="34"/>
       <c r="J27" s="34"/>
       <c r="K27" s="33"/>
-      <c r="O27" s="30"/>
+      <c r="O27" s="31"/>
       <c r="S27" s="6"/>
       <c r="U27" s="32"/>
       <c r="X27" s="33"/>
@@ -2521,7 +2561,7 @@
       <c r="AG27" s="6"/>
     </row>
     <row r="28">
-      <c r="A28" s="27"/>
+      <c r="A28" s="28"/>
       <c r="D28" s="35"/>
       <c r="H28" s="34"/>
       <c r="I28" s="34"/>
@@ -2534,7 +2574,7 @@
       <c r="AG28" s="6"/>
     </row>
     <row r="29">
-      <c r="A29" s="27"/>
+      <c r="A29" s="28"/>
       <c r="D29" s="35"/>
       <c r="H29" s="34"/>
       <c r="I29" s="34"/>
@@ -2547,9 +2587,9 @@
       <c r="AG29" s="6"/>
     </row>
     <row r="30">
-      <c r="A30" s="27"/>
-      <c r="D30" s="30"/>
-      <c r="K30" s="31"/>
+      <c r="A30" s="28"/>
+      <c r="D30" s="31"/>
+      <c r="K30" s="18"/>
       <c r="U30" s="35"/>
       <c r="AD30" s="6"/>
       <c r="AE30" s="6"/>
@@ -2557,9 +2597,9 @@
       <c r="AG30" s="6"/>
     </row>
     <row r="31">
-      <c r="A31" s="27"/>
-      <c r="F31" s="31"/>
-      <c r="K31" s="31"/>
+      <c r="A31" s="28"/>
+      <c r="F31" s="18"/>
+      <c r="K31" s="18"/>
       <c r="S31" s="6"/>
       <c r="T31" s="11"/>
       <c r="AD31" s="6"/>
@@ -2568,9 +2608,9 @@
       <c r="AG31" s="6"/>
     </row>
     <row r="32">
-      <c r="A32" s="27"/>
-      <c r="F32" s="31"/>
-      <c r="K32" s="31"/>
+      <c r="A32" s="28"/>
+      <c r="F32" s="18"/>
+      <c r="K32" s="18"/>
       <c r="M32" s="36"/>
       <c r="R32" s="11"/>
       <c r="S32" s="6"/>
@@ -2581,9 +2621,9 @@
       <c r="AG32" s="6"/>
     </row>
     <row r="33">
-      <c r="A33" s="27"/>
-      <c r="F33" s="31"/>
-      <c r="K33" s="31"/>
+      <c r="A33" s="28"/>
+      <c r="F33" s="18"/>
+      <c r="K33" s="18"/>
       <c r="M33" s="36"/>
       <c r="R33" s="11"/>
       <c r="S33" s="6"/>
@@ -8582,7 +8622,7 @@
         <v>16</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="R1" s="6" t="s">
         <v>18</v>
@@ -8618,209 +8658,212 @@
         <v>29</v>
       </c>
       <c r="AC1" s="38" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AD1" s="39" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="AE1" s="39" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AF1" s="39" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="AG1" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="AH1" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="AI1" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="AJ1" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK1" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="AL1" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM1" s="27" t="s">
-        <v>152</v>
+        <v>153</v>
+      </c>
+      <c r="AH1" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI1" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ1" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK1" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL1" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM1" s="28" t="s">
+        <v>159</v>
       </c>
       <c r="AN1" s="39" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AO1" s="39" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="AP1" s="39" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AQ1" s="39" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="AR1" s="39" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="AS1" s="39" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AT1" s="40" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AU1" s="40" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="AV1" s="40" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AW1" s="41" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AX1" s="42" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AY1" s="42" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AZ1" s="43" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="BA1" s="43" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="BB1" s="43" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="BC1" s="43" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="BD1" s="43" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="BE1" s="43" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="BF1" s="43" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="BG1" s="43" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="BH1" s="43" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="BI1" s="43" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="s">
-        <v>175</v>
+      <c r="A2" s="18" t="s">
+        <v>182</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="Q2" s="39" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="R2" s="39" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="S2" s="39" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="U2" s="39" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="X2" s="39" t="s">
-        <v>188</v>
+        <v>195</v>
+      </c>
+      <c r="Y2" s="39" t="s">
+        <v>196</v>
       </c>
       <c r="AD2" s="39" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AE2" s="39" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="AF2" s="39" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="AG2" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="AH2" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="AI2" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="AJ2" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="AK2" s="27"/>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="AH2" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI2" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="AJ2" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28" t="s">
+        <v>204</v>
       </c>
       <c r="AN2" s="44" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="AO2" s="45" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AP2" s="39" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AQ2" s="39" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="AR2" s="46" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AS2" s="39" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AT2" s="39" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AU2" s="39" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="AV2" s="39" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AW2" s="39" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AX2" s="39" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AY2" s="39" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AZ2" s="39">
         <v>3.2323232E7</v>
@@ -8834,7 +8877,7 @@
       <c r="BG2" s="39"/>
       <c r="BH2" s="39"/>
       <c r="BI2" s="39" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
